--- a/backend/AP_Dynasty_Backend.xlsx
+++ b/backend/AP_Dynasty_Backend.xlsx
@@ -2337,10 +2337,8 @@
       <c r="D29" s="46" t="n">
         <v>2015</v>
       </c>
-      <c r="E29" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E29" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F29" s="46" t="n"/>
       <c r="G29" s="46" t="n"/>
@@ -2504,10 +2502,8 @@
       <c r="D32" s="46" t="n">
         <v>2015</v>
       </c>
-      <c r="E32" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E32" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F32" s="46" t="n"/>
       <c r="G32" s="46" t="n"/>
@@ -3394,10 +3390,8 @@
       <c r="D48" s="13" t="n">
         <v>2015</v>
       </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E48" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F48" s="13" t="n"/>
       <c r="G48" s="13" t="n"/>
@@ -4801,10 +4795,8 @@
       <c r="D73" s="13" t="n">
         <v>2016</v>
       </c>
-      <c r="E73" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E73" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="13" t="n"/>
@@ -4913,10 +4905,8 @@
       <c r="D75" s="13" t="n">
         <v>2016</v>
       </c>
-      <c r="E75" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E75" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F75" s="13" t="n"/>
       <c r="G75" s="13" t="n"/>
@@ -7399,10 +7389,8 @@
       <c r="D119" s="46" t="n">
         <v>2018</v>
       </c>
-      <c r="E119" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E119" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F119" s="46" t="n"/>
       <c r="G119" s="46" t="n"/>
@@ -8788,10 +8776,8 @@
       <c r="D144" s="46" t="n">
         <v>2019</v>
       </c>
-      <c r="E144" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E144" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F144" s="46" t="n"/>
       <c r="G144" s="46" t="n"/>
@@ -8834,7 +8820,7 @@
       </c>
       <c r="B145" s="46" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C145" s="46" t="inlineStr">
@@ -8950,7 +8936,7 @@
       </c>
       <c r="B147" s="46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C147" s="46" t="inlineStr">
@@ -9071,10 +9057,8 @@
       <c r="D149" s="13" t="n">
         <v>2019</v>
       </c>
-      <c r="E149" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E149" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F149" s="13" t="n"/>
       <c r="G149" s="13" t="n"/>
@@ -9632,7 +9616,7 @@
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
@@ -9748,7 +9732,7 @@
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
@@ -10765,10 +10749,8 @@
       <c r="D179" s="13" t="n">
         <v>2020</v>
       </c>
-      <c r="E179" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E179" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F179" s="13" t="n"/>
       <c r="G179" s="13" t="n"/>
@@ -11261,7 +11243,7 @@
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
@@ -13510,10 +13492,8 @@
       <c r="D228" s="46" t="n">
         <v>2022</v>
       </c>
-      <c r="E228" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E228" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F228" s="46" t="n"/>
       <c r="G228" s="46" t="n"/>
@@ -13679,10 +13659,8 @@
       <c r="D231" s="46" t="n">
         <v>2022</v>
       </c>
-      <c r="E231" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E231" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F231" s="46" t="n"/>
       <c r="G231" s="46" t="n"/>
@@ -14471,10 +14449,8 @@
       <c r="D245" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="E245" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E245" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="F245" s="13" t="n"/>
       <c r="G245" s="13" t="n"/>
@@ -15084,10 +15060,8 @@
       <c r="D256" s="46" t="n">
         <v>2023</v>
       </c>
-      <c r="E256" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E256" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F256" s="46" t="n"/>
       <c r="G256" s="46" t="n"/>
@@ -15251,10 +15225,8 @@
       <c r="D259" s="46" t="n">
         <v>2023</v>
       </c>
-      <c r="E259" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E259" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F259" s="46" t="n"/>
       <c r="G259" s="46" t="n"/>
@@ -18260,7 +18232,7 @@
       </c>
       <c r="B313" s="46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C313" s="46" t="inlineStr">
@@ -18271,10 +18243,8 @@
       <c r="D313" s="46" t="n">
         <v>2025</v>
       </c>
-      <c r="E313" s="46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E313" s="46" t="n">
+        <v>8</v>
       </c>
       <c r="F313" s="46" t="n"/>
       <c r="G313" s="46" t="n"/>
@@ -19568,7 +19538,7 @@
       </c>
       <c r="B341" s="46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C341" s="46" t="inlineStr">
